--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -2569,30 +2569,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jannik</t>
+          <t>JayJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M4DMAX</t>
+          <t>Suflah</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
-        <is>
-          <t>Joy</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Suflah</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>JayJ</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
         <is>
           <t>Laves</t>
         </is>

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -308,7 +308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,6 +544,16 @@
           <t>Bodo Glimt</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Duduka</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Luqueta</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,11 +593,6 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Duduka</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
           <t>Nightrise</t>
         </is>
       </c>
@@ -775,35 +780,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Luqueta</t>
+          <t>Lopes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lopes</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>sobrunin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>sobrunin</t>
+          <t>Coutinho</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
-        <is>
-          <t>Coutinho</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>Kaos</t>
         </is>
@@ -1545,25 +1545,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Soulless</t>
+          <t>gyukaa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>gyukaa</t>
+          <t>KNZWY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KNZWY</t>
+          <t>Zé Leão</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>Zé Leão</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>Icexit</t>
         </is>
@@ -1600,6 +1595,11 @@
           <t>Tuk</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Soulless</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1778,6 +1778,11 @@
           <t>Miojinho</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>qweqawq</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1810,6 +1815,11 @@
           <t>Purikywa</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>th ˆˆ</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2582,6 +2592,11 @@
           <t>Laves</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Odysseys</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3123,6 +3138,16 @@
           <t>Fatox</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Mtr</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>psч</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3155,6 +3180,16 @@
           <t>MpaToh</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ayslan loves L</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>O CALVINISTA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3298,6 +3333,11 @@
           <t>yonaha</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>lule</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3672,6 +3712,16 @@
           <t>marimoon</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ScherBi</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Melousa</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3951,6 +4001,38 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>Wishful</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>sixa_eaters</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Get Is</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Duarte</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>dgo</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>dnk</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>nickzinn</t>
         </is>
       </c>
     </row>

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -308,7 +308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -425,7 +425,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Borrachinha</t>
+          <t>zuw</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaname</t>
+          <t>Kozolove</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kozolove</t>
+          <t>Zerando</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>loverman</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>draCo</t>
         </is>
       </c>
     </row>
@@ -2913,6 +2928,11 @@
           <t>wpv</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>salem</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4033,6 +4053,122 @@
       <c r="F98" t="inlineStr">
         <is>
           <t>nickzinn</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kaname</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>raining stars</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>dudinhal</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Mey</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DavyJones</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>kissa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GalinhaMamifera</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>drk</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>gL X</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Hast</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ferRomantica</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Borrachinha</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kafaja</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Fael</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>rahg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>aQc</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Eraj</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Kossar Osako</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>lucKZin</t>
         </is>
       </c>
     </row>

--- a/dados_excel/teams.xlsx
+++ b/dados_excel/teams.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Queijo Coallho</t>
+          <t>Marelo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Filiceta</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>spx</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
